--- a/branches/main/ValueSet-mii-vs-icu-code-monitoring-und-vitaldaten-loinc.xlsx
+++ b/branches/main/ValueSet-mii-vs-icu-code-monitoring-und-vitaldaten-loinc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="140">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.3</t>
+    <t>2027.0.0-ballot.3-rc.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -105,7 +105,7 @@
     <t>8867-4</t>
   </si>
   <si>
-    <t>Heart Rate</t>
+    <t>Heart rate</t>
   </si>
   <si>
     <t>8480-6</t>
@@ -330,6 +330,12 @@
     <t>Body height</t>
   </si>
   <si>
+    <t>8306-3</t>
+  </si>
+  <si>
+    <t>Body height --lying</t>
+  </si>
+  <si>
     <t>8303-0</t>
   </si>
   <si>
@@ -405,10 +411,13 @@
     <t>60838-0</t>
   </si>
   <si>
+    <t>Nasopharyngeal temperature</t>
+  </si>
+  <si>
+    <t>104063-3</t>
+  </si>
+  <si>
     <t>Body temperature</t>
-  </si>
-  <si>
-    <t>104063-3</t>
   </si>
   <si>
     <t>60825-7</t>
@@ -687,7 +696,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1115,31 +1124,39 @@
         <v>131</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
